--- a/jogos_2025-04-14.xlsx
+++ b/jogos_2025-04-14.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['33', '63']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['5', '52', '85', '89', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['66']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45761.45833333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,16 +1030,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
         <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD5" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AI5" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45761.45833333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1188,80 +1188,80 @@
         <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>2.6</v>
       </c>
       <c r="P6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['33', '63']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['5', '52', '85', '89', '90+4']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AI6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45761.45833333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>4.39</v>
       </c>
       <c r="N9" t="n">
-        <v>4.75</v>
+        <v>7.35</v>
       </c>
       <c r="O9" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
         <v>1.04</v>
@@ -1608,47 +1608,47 @@
         <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AB9" t="n">
         <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45761.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,23 +1675,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>4.39</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>7.35</v>
+        <v>4.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="T10" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V10" t="n">
         <v>1.04</v>
@@ -1737,47 +1737,47 @@
         <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
         <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45761.5</v>
@@ -1923,119 +1923,119 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['50', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.25</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AH12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45761.54166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>9.300000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>5.03</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.08</v>
+        <v>2.37</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AD13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['53', '67']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['7', '36', '78']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45761.54166666666</v>
@@ -2181,32 +2181,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>3.09</v>
+        <v>2.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.88</v>
+        <v>2.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['41', '54']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['68', '71']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45761.54166666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Sloboda Užice</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
         <v>2.7</v>
       </c>
       <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.75</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['39', '46']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.04</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AH15" t="n">
         <v>3.2</v>
       </c>
-      <c r="Y15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AI15" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45761.54166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sloboda Užice</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>1.48</v>
-      </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
         <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Z16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['39', '46']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AI16" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45761.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.77</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.66</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['7', '36', '78']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['50', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45761.54166666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.01</v>
+        <v>2.96</v>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.03</v>
+        <v>3.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>3.09</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="X18" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>3.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="n">
         <v>2.15</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['53', '67']</t>
+          <t>['41', '54']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68', '71']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.97</v>
+        <v>1.45</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45761.54166666666</v>
@@ -2955,35 +2955,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="O20" t="n">
-        <v>3.94</v>
+        <v>2.65</v>
       </c>
       <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Z20" t="n">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.56</v>
+        <v>3.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45761.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.65</v>
+        <v>2.74</v>
       </c>
       <c r="O21" t="n">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['72', '90+1', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['33', '42']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['42', '48', '71']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45761.58333333334</v>
@@ -3213,32 +3213,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,65 +3249,65 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.43</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.85</v>
+        <v>6.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.26</v>
+        <v>6.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.93</v>
+        <v>2.68</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>3.62</v>
+        <v>2.97</v>
       </c>
       <c r="Y22" t="n">
         <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['4', '18', '41', '44']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45761.58333333334</v>
@@ -3342,35 +3342,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,80 +3378,80 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X23" t="n">
         <v>2.84</v>
       </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.9</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['72', '90+1', '90+3']</t>
+          <t>['8', '88']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['33', '42']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AJ23" t="n">
         <v>2.3</v>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
         <v>1</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.28</v>
+        <v>2.91</v>
       </c>
       <c r="N24" t="n">
-        <v>2.68</v>
+        <v>2.21</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
         <v>1.06</v>
       </c>
       <c r="W24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['3', '15']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.33</v>
       </c>
-      <c r="X24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45761.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S25" t="n">
         <v>3.2</v>
       </c>
-      <c r="M25" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="O25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T25" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.2</v>
+        <v>2.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['3', '15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['42', '48', '71']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45761.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,91 +3739,91 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['4', '18', '41', '44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45761.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Adanaspor</t>
+          <t>Hebar 1918</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.89</v>
+        <v>11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="O27" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.44</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3957,20 +3957,20 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['18', '61', '86']</t>
+          <t>['78', '90']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>2.65</v>
+        <v>1.11</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AI27" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45761.58333333334</v>
@@ -3987,119 +3987,119 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Adanaspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>4.89</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>6.1</v>
+        <v>1.58</v>
       </c>
       <c r="O28" t="n">
-        <v>1.91</v>
+        <v>6.5</v>
       </c>
       <c r="P28" t="n">
         <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U28" t="n">
         <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
         <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '61', '86']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>2.65</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.7</v>
+        <v>1.07</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45761.58333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hebar 1918</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Yeni Malatyaspor</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N29" t="n">
-        <v>1.14</v>
+        <v>26.15</v>
       </c>
       <c r="O29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '20', '41', '45', '57', '76', '88']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['78', '90']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45761.58333333334</v>
@@ -4374,32 +4374,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yeni Malatyaspor</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>3.28</v>
       </c>
       <c r="N31" t="n">
-        <v>26.15</v>
+        <v>2.68</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['7', '20', '41', '45', '57', '76', '88']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45761.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI33" t="n">
         <v>2</v>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['8', '88']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45761.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4915,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="M35" t="n">
-        <v>3.47</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="P35" t="n">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.65</v>
+        <v>4.44</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>2.73</v>
+        <v>3.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.89</v>
+        <v>2.16</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="X35" t="n">
-        <v>3.24</v>
+        <v>5.15</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.98</v>
+        <v>1.49</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.53</v>
+        <v>2.19</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.77</v>
+        <v>2.51</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45761.60416666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5044,7 +5044,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>3.47</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O36" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="P36" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.44</v>
+        <v>5.65</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="T36" t="n">
-        <v>2.16</v>
+        <v>2.89</v>
       </c>
       <c r="U36" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="X36" t="n">
-        <v>5.15</v>
+        <v>3.24</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.49</v>
+        <v>1.98</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.19</v>
+        <v>3.53</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AC36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AI36" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD36" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['51']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45761.60416666666</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.4</v>
+        <v>1.82</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="O37" t="n">
-        <v>3.75</v>
+        <v>2.39</v>
       </c>
       <c r="P37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['9', '26']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45761.625</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.82</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="R38" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="T38" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X38" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['9', '26']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45761.625</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="M39" t="n">
         <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="O39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3.2</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S39" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['9', '81', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['29', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['80']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45761.625</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="P40" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X40" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AD40" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['9', '81', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['29', '90+4']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45761.625</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G42" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
         <v>1</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>8</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y42" t="n">
         <v>2</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.42</v>
-      </c>
       <c r="Z42" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AA42" t="n">
-        <v>5.25</v>
+        <v>3.34</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['90+7']</t>
+          <t>['9', '55', '57']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '75']</t>
         </is>
       </c>
       <c r="AG42" t="n">
         <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AJ42" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45761.64583333334</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,16 +5932,16 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Legnago Salus</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>3.53</v>
+        <v>4.4</v>
       </c>
       <c r="O43" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S43" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="T43" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="X43" t="n">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
+          <t>['90+7']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45761.64583333334</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,109 +6061,109 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Legnago Salus</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P44" t="n">
         <v>2</v>
       </c>
-      <c r="I44" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M44" t="n">
-        <v>4</v>
-      </c>
-      <c r="N44" t="n">
-        <v>8</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.24</v>
-      </c>
       <c r="Q44" t="n">
-        <v>5.9</v>
+        <v>4.25</v>
       </c>
       <c r="R44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.32</v>
       </c>
-      <c r="S44" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.26</v>
-      </c>
       <c r="X44" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1.83</v>
       </c>
-      <c r="AA44" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['9', '55', '57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['34', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AJ44" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45761.64583333334</v>
@@ -6567,29 +6567,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -6603,55 +6603,55 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.44</v>
+        <v>2.69</v>
       </c>
       <c r="M48" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="N48" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P48" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T48" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>2.68</v>
+        <v>1.06</v>
       </c>
       <c r="W48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB48" t="n">
         <v>1.28</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.35</v>
       </c>
       <c r="AC48" t="n">
         <v>1.73</v>
@@ -6661,25 +6661,25 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI48" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45761.66666666666</v>
@@ -6696,29 +6696,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -6732,55 +6732,55 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.69</v>
+        <v>3.44</v>
       </c>
       <c r="M49" t="n">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="N49" t="n">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="O49" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S49" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T49" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U49" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V49" t="n">
-        <v>1.06</v>
+        <v>2.68</v>
       </c>
       <c r="W49" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X49" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AC49" t="n">
         <v>1.73</v>
@@ -6790,25 +6790,25 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45761.66666666666</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,25 +7996,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N59" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="O59" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="P59" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="R59" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S59" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T59" t="n">
         <v>3</v>
       </c>
       <c r="U59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W59" t="n">
         <v>1.36</v>
       </c>
-      <c r="V59" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X59" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AB59" t="n">
         <v>1.25</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['11', '23', '32']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AI59" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45761.77083333334</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,25 +8125,25 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G60" t="n">
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="M60" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="O60" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="P60" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="R60" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S60" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T60" t="n">
         <v>3</v>
       </c>
       <c r="U60" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V60" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W60" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X60" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB60" t="n">
         <v>1.25</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AD60" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>['11', '23', '32']</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
         <v>1.75</v>
       </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>['7']</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AG60" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AH60" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AI60" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45761.77083333334</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,22 +8383,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -8409,83 +8409,83 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
         <v>3.4</v>
       </c>
       <c r="O62" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S62" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q62" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3</v>
-      </c>
       <c r="T62" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="U62" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V62" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W62" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="X62" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="Y62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI62" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z62" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>['26', '28', '87']</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG62" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ62" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45761.79166666666</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,22 +8512,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="M63" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
         <v>3.4</v>
       </c>
       <c r="O63" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P63" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R63" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S63" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="T63" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U63" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="V63" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W63" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="X63" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AA63" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AD63" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>['26', '28', '87']</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH63" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG63" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AI63" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45761.79166666666</v>
@@ -9028,19 +9028,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -9054,22 +9054,22 @@
         </is>
       </c>
       <c r="L67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M67" t="n">
         <v>3.4</v>
       </c>
-      <c r="M67" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N67" t="n">
-        <v>2.25</v>
+        <v>5.75</v>
       </c>
       <c r="O67" t="n">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="R67" t="n">
         <v>1.57</v>
@@ -9084,31 +9084,31 @@
         <v>1.25</v>
       </c>
       <c r="V67" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W67" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X67" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA67" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9117,20 +9117,20 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AI67" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45761.88541666666</v>
@@ -9157,19 +9157,19 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -9183,22 +9183,22 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>5.75</v>
+        <v>2.25</v>
       </c>
       <c r="O68" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="P68" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="R68" t="n">
         <v>1.57</v>
@@ -9213,53 +9213,53 @@
         <v>1.25</v>
       </c>
       <c r="V68" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W68" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X68" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y68" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG68" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI68" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z68" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>['71']</t>
-        </is>
-      </c>
-      <c r="AG68" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ68" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45761.88541666666</v>
